--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff72c23a235
+	0x7ff72bf92630
+	0x7ff72bd216dd
+	0x7ff72bd7a27e
+	0x7ff72bd7a58c
+	0x7ff72bdced77
+	0x7ff72bdcbaba
+	0x7ff72bd6b0ed
+	0x7ff72bd6bf63
+	0x7ff72c265d60
+	0x7ff72c25fe8a
+	0x7ff72c281005
+	0x7ff72bfad71e
+	0x7ff72bfb4e1f
+	0x7ff72bf9b7c4
+	0x7ff72bf9b97f
+	0x7ff72bf818e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff71758a235
-	0x7ff7172e2630
-	0x7ff7170716dd
-	0x7ff7170ca27e
-	0x7ff7170ca58c
-	0x7ff71711ed77
-	0x7ff71711baba
-	0x7ff7170bb0ed
-	0x7ff7170bbf63
-	0x7ff7175b5d60
-	0x7ff7175afe8a
-	0x7ff7175d1005
-	0x7ff7172fd71e
-	0x7ff717304e1f
-	0x7ff7172eb7c4
-	0x7ff7172eb97f
-	0x7ff7172d18e8
+	0x7ff7fd82a235
+	0x7ff7fd582630
+	0x7ff7fd3116dd
+	0x7ff7fd36a27e
+	0x7ff7fd36a58c
+	0x7ff7fd3bed77
+	0x7ff7fd3bbaba
+	0x7ff7fd35b0ed
+	0x7ff7fd35bf63
+	0x7ff7fd855d60
+	0x7ff7fd84fe8a
+	0x7ff7fd871005
+	0x7ff7fd59d71e
+	0x7ff7fd5a4e1f
+	0x7ff7fd58b7c4
+	0x7ff7fd58b97f
+	0x7ff7fd5718e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
